--- a/SeleniumTests/TestDataFolder/ReportTestDataPaging.xlsx
+++ b/SeleniumTests/TestDataFolder/ReportTestDataPaging.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C498DEA-1761-44A2-874C-4069A0B03D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BB4341-7223-4858-BA02-51C28DD46EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29730" yWindow="5520" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReportInfoTestData" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
     <t>To Date</t>
   </si>
   <si>
-    <t>Doc Type</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -75,6 +72,9 @@
   </si>
   <si>
     <t>Page Number</t>
+  </si>
+  <si>
+    <t>Document Type</t>
   </si>
 </sst>
 </file>
@@ -394,42 +394,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -438,7 +449,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>2026</v>
@@ -447,10 +458,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -462,45 +473,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D090C9CC-5C92-4403-A19E-2A9D47258D4C}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -509,7 +532,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>2026</v>
@@ -518,10 +541,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>100</v>
@@ -536,45 +559,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5A9398-25F8-4D63-B959-AB4CABB96635}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -583,7 +618,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>2026</v>
@@ -592,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
         <v>3</v>
